--- a/data/Financeiro_BAM_Fase1_BI.xlsx
+++ b/data/Financeiro_BAM_Fase1_BI.xlsx
@@ -9147,13 +9147,17 @@
         </is>
       </c>
       <c r="D30" s="473" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="E30" s="472" t="n">
         <v>25</v>
       </c>
       <c r="F30" s="472" t="n"/>
-      <c r="G30" s="472" t="n"/>
+      <c r="G30" s="472" t="inlineStr">
+        <is>
+          <t>PAGO</t>
+        </is>
+      </c>
       <c r="H30" s="472" t="n"/>
       <c r="I30" s="472" t="n"/>
     </row>
